--- a/Output Data Tables/AFAT Outputs/Aggregated Tables/2024/Airline_Profitability_Statistics_2024.xlsx
+++ b/Output Data Tables/AFAT Outputs/Aggregated Tables/2024/Airline_Profitability_Statistics_2024.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="34" uniqueCount="34">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -148,7 +160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -164,19 +176,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2">
@@ -644,18 +656,98 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>4695211230</v>
+      </c>
+      <c r="C25" s="0">
+        <v>0.0057000000000000106</v>
+      </c>
+      <c r="D25" s="0">
+        <v>8.1799999999999784</v>
+      </c>
+      <c r="E25" s="0">
+        <v>0.0068000000000000005</v>
+      </c>
+      <c r="F25" s="0">
+        <v>9.7200000000000273</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>-1366566040</v>
+      </c>
+      <c r="C26" s="0">
+        <v>-0.0040999999999999925</v>
+      </c>
+      <c r="D26" s="0">
+        <v>-3.9800000000000182</v>
+      </c>
+      <c r="E26" s="0">
+        <v>-0.0050000000000000044</v>
+      </c>
+      <c r="F26" s="0">
+        <v>-5.0699999999999932</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>-1192264830</v>
+      </c>
+      <c r="C27" s="0">
+        <v>-0.0097000000000000003</v>
+      </c>
+      <c r="D27" s="0">
+        <v>-9.2000000000000028</v>
+      </c>
+      <c r="E27" s="0">
+        <v>-0.0121</v>
+      </c>
+      <c r="F27" s="0">
+        <v>-11.659999999999982</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>89098510</v>
+      </c>
+      <c r="C28" s="0">
+        <v>0.0011999999999999789</v>
+      </c>
+      <c r="D28" s="0">
+        <v>0.56000000000000227</v>
+      </c>
+      <c r="E28" s="0">
+        <v>0.0015000000000000013</v>
+      </c>
+      <c r="F28" s="0">
+        <v>0.70000000000000284</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>2225478870</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>0.0017000000000000071</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>1.8400000000000034</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>0.0020000000000000018</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>2.2599999999999909</v>
       </c>
     </row>
